--- a/Server/data/leads.xlsx
+++ b/Server/data/leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F21"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -507,9 +507,329 @@
         <v>15/4/2026, 6:13:03 pm</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B6" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C6" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E6" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F6" t="str">
+        <v>16/4/2026, 9:37:42 am</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B7" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C7" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Free AMH Test</v>
+      </c>
+      <c r="E7" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F7" t="str">
+        <v>16/4/2026, 9:47:17 am</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B8" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D8" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E8" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F8" t="str">
+        <v>16/4/2026, 9:52:39 am</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B9" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D9" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E9" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F9" t="str">
+        <v>16/4/2026, 10:04:11 am</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B10" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Free AMH Test</v>
+      </c>
+      <c r="E10" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F10" t="str">
+        <v>16/4/2026, 10:10:49 am</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B11" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C11" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E11" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F11" t="str">
+        <v>16/4/2026, 10:14:44 am</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B12" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C12" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D12" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E12" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F12" t="str">
+        <v>16/4/2026, 10:15:28 am</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B13" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C13" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E13" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F13" t="str">
+        <v>16/4/2026, 10:19:23 am</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B14" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C14" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D14" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E14" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F14" t="str">
+        <v>16/4/2026, 10:24:31 am</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B15" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C15" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Free Ultrasound / 50% Off on AMH OR Semen Test</v>
+      </c>
+      <c r="E15" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F15" t="str">
+        <v>16/4/2026, 10:36:10 am</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B16" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C16" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E16" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F16" t="str">
+        <v>16/4/2026, 10:45:19 am</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B17" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C17" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Free Ultrasound / 50% Off on AMH OR Semen Test</v>
+      </c>
+      <c r="E17" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F17" t="str">
+        <v>16/4/2026, 10:46:41 am</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B18" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C18" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D18" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E18" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F18" t="str">
+        <v>16/4/2026, 10:49:05 am</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B19" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C19" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D19" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E19" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F19" t="str">
+        <v>16/4/2026, 10:50:08 am</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B20" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C20" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E20" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F20" t="str">
+        <v>16/4/2026, 10:52:46 am</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B21" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C21" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E21" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F21" t="str">
+        <v>16/4/2026, 10:57:09 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Server/data/leads.xlsx
+++ b/Server/data/leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F29"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -827,9 +827,169 @@
         <v>16/4/2026, 10:57:09 am</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B22" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C22" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Free Ultrasound / 50% Off on AMH OR Semen Test</v>
+      </c>
+      <c r="E22" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F22" t="str">
+        <v>16/4/2026, 11:04:12 am</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Patel Car</v>
+      </c>
+      <c r="B23" t="str">
+        <v>patelcars1902@gmail.com</v>
+      </c>
+      <c r="C23" t="str">
+        <v>9900990999</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E23" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F23" t="str">
+        <v>16/4/2026, 12:20:55 pm</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Patel Cars</v>
+      </c>
+      <c r="B24" t="str">
+        <v>patelcars12@gmail.com</v>
+      </c>
+      <c r="C24" t="str">
+        <v>9900990000</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2nd Consultation free / 20% Off on Medicine</v>
+      </c>
+      <c r="E24" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F24" t="str">
+        <v>16/4/2026, 12:21:30 pm</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Patel Cars</v>
+      </c>
+      <c r="B25" t="str">
+        <v>patelcars1o2@gmail.com</v>
+      </c>
+      <c r="C25" t="str">
+        <v>9900990900</v>
+      </c>
+      <c r="D25" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E25" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F25" t="str">
+        <v>16/4/2026, 12:22:20 pm</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B26" t="str">
+        <v>tiwariabhishek990@gmail.com</v>
+      </c>
+      <c r="C26" t="str">
+        <v>06398009878</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Free AMH Test</v>
+      </c>
+      <c r="E26" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F26" t="str">
+        <v>16/4/2026, 12:38:47 pm</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B27" t="str">
+        <v>tiwariabhiek990@gmail.com</v>
+      </c>
+      <c r="C27" t="str">
+        <v>06398082878</v>
+      </c>
+      <c r="D27" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E27" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F27" t="str">
+        <v>16/4/2026, 12:40:03 pm</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B28" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C28" t="str">
+        <v>06398002878</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Free Ultrasound / 50% Off on AMH OR Semen Test</v>
+      </c>
+      <c r="E28" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F28" t="str">
+        <v>16/4/2026, 12:43:53 pm</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B29" t="str">
+        <v>tiwariabhishek900@gmail.com</v>
+      </c>
+      <c r="C29" t="str">
+        <v>06398002870</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Free AMH Test</v>
+      </c>
+      <c r="E29" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F29" t="str">
+        <v>16/4/2026, 12:45:16 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F29"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Server/data/leads.xlsx
+++ b/Server/data/leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F37"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -987,9 +987,169 @@
         <v>16/4/2026, 12:45:16 pm</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Abhishek</v>
+      </c>
+      <c r="B30" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C30" t="str">
+        <v>6398002878</v>
+      </c>
+      <c r="D30" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E30" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F30" t="str">
+        <v>16/4/2026, 1:43:32 pm</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B31" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C31" t="str">
+        <v>6398002878</v>
+      </c>
+      <c r="D31" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E31" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F31" t="str">
+        <v>16/4/2026, 2:02:38 pm</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B32" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C32" t="str">
+        <v>6398002878</v>
+      </c>
+      <c r="D32" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E32" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F32" t="str">
+        <v>16/4/2026, 2:03:54 pm</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B33" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C33" t="str">
+        <v>6398002878</v>
+      </c>
+      <c r="D33" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E33" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F33" t="str">
+        <v>16/4/2026, 3:21:08 pm</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B34" t="str">
+        <v>tiwariabhishek9900@gmail.com</v>
+      </c>
+      <c r="C34" t="str">
+        <v>6398002878</v>
+      </c>
+      <c r="D34" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E34" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F34" t="str">
+        <v>16/4/2026, 3:23:32 pm</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Patel Cars</v>
+      </c>
+      <c r="B35" t="str">
+        <v>patelcars1982@gmail.com</v>
+      </c>
+      <c r="C35" t="str">
+        <v>9900990099</v>
+      </c>
+      <c r="D35" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E35" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F35" t="str">
+        <v>16/4/2026, 3:29:37 pm</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Patel Cars</v>
+      </c>
+      <c r="B36" t="str">
+        <v>patelcars1982@gmail.com</v>
+      </c>
+      <c r="C36" t="str">
+        <v>9900990099</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Free Ultrasound / 50% Off on AMH OR Semen Test</v>
+      </c>
+      <c r="E36" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F36" t="str">
+        <v>16/4/2026, 3:30:36 pm</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Patel Cars</v>
+      </c>
+      <c r="B37" t="str">
+        <v>patelcars19821@gmail.com</v>
+      </c>
+      <c r="C37" t="str">
+        <v>9900990090</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Free AMH Test</v>
+      </c>
+      <c r="E37" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F37" t="str">
+        <v>16/4/2026, 3:40:44 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F37"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Server/data/leads.xlsx
+++ b/Server/data/leads.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -1147,9 +1147,29 @@
         <v>16/4/2026, 3:40:44 pm</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Abhishek Tiwari</v>
+      </c>
+      <c r="B38" t="str">
+        <v>abhi@gmail.com</v>
+      </c>
+      <c r="C38" t="str">
+        <v>6398002879</v>
+      </c>
+      <c r="D38" t="str">
+        <v>15% off on Medicine / 20% off on Blood Test</v>
+      </c>
+      <c r="E38" t="str">
+        <v>spin-wheel-app</v>
+      </c>
+      <c r="F38" t="str">
+        <v>16/4/2026, 4:10:00 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F38"/>
   </ignoredErrors>
 </worksheet>
 </file>